--- a/reports/tables/top5_methods_for_manuscript_pretty.xlsx
+++ b/reports/tables/top5_methods_for_manuscript_pretty.xlsx
@@ -535,46 +535,46 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.4855</v>
+        <v>0.5392</v>
       </c>
       <c r="E2" t="n">
-        <v>0.7817</v>
+        <v>0.7254</v>
       </c>
       <c r="F2" t="n">
-        <v>0.4665</v>
+        <v>0.5272</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0862</v>
+        <v>0.08989999999999999</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9708</v>
+        <v>0.9676</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1552</v>
+        <v>0.1599</v>
       </c>
       <c r="J2" t="n">
-        <v>0.6539</v>
+        <v>0.6568000000000001</v>
       </c>
       <c r="K2" t="n">
-        <v>0.147</v>
+        <v>0.1408</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1949</v>
+        <v>0.1944</v>
       </c>
       <c r="M2" t="n">
-        <v>0.4228</v>
+        <v>0.4564</v>
       </c>
       <c r="N2" t="n">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="O2" t="n">
-        <v>1177</v>
+        <v>1043</v>
       </c>
       <c r="P2" t="n">
-        <v>1029</v>
+        <v>1163</v>
       </c>
       <c r="Q2" t="n">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
@@ -597,46 +597,46 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.5149</v>
+        <v>0.5579</v>
       </c>
       <c r="E3" t="n">
-        <v>0.8028</v>
+        <v>0.7324000000000001</v>
       </c>
       <c r="F3" t="n">
-        <v>0.4964</v>
+        <v>0.5467</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0931</v>
+        <v>0.09420000000000001</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9751</v>
+        <v>0.9695</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1668</v>
+        <v>0.1669</v>
       </c>
       <c r="J3" t="n">
-        <v>0.6861</v>
+        <v>0.6838</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1414</v>
+        <v>0.1369</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2155</v>
+        <v>0.215</v>
       </c>
       <c r="M3" t="n">
-        <v>0.4751</v>
+        <v>0.4861</v>
       </c>
       <c r="N3" t="n">
-        <v>114</v>
+        <v>104</v>
       </c>
       <c r="O3" t="n">
-        <v>1111</v>
+        <v>1000</v>
       </c>
       <c r="P3" t="n">
-        <v>1095</v>
+        <v>1206</v>
       </c>
       <c r="Q3" t="n">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
@@ -650,59 +650,59 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>XGBoost</t>
+          <t>RandomForest</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Borderline-SMOTE</t>
+          <t>No synthetic resampling</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.6614</v>
+        <v>0.5149</v>
       </c>
       <c r="E4" t="n">
-        <v>0.5845</v>
+        <v>0.7465000000000001</v>
       </c>
       <c r="F4" t="n">
-        <v>0.6664</v>
+        <v>0.5</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1013</v>
+        <v>0.0877</v>
       </c>
       <c r="H4" t="n">
-        <v>0.9614</v>
+        <v>0.9684</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1727</v>
+        <v>0.1569</v>
       </c>
       <c r="J4" t="n">
-        <v>0.655</v>
+        <v>0.6536</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1244</v>
+        <v>0.1189</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0687</v>
+        <v>0.0635</v>
       </c>
       <c r="M4" t="n">
-        <v>0.16</v>
+        <v>0.1247</v>
       </c>
       <c r="N4" t="n">
-        <v>83</v>
+        <v>106</v>
       </c>
       <c r="O4" t="n">
-        <v>736</v>
+        <v>1103</v>
       </c>
       <c r="P4" t="n">
-        <v>1470</v>
+        <v>1103</v>
       </c>
       <c r="Q4" t="n">
-        <v>59</v>
+        <v>36</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>{'model__subsample': 1.0, 'model__n_estimators': 300, 'model__max_depth': 5, 'model__learning_rate': 0.01, 'model__colsample_bytree': 1.0}</t>
+          <t>{'model__n_estimators': 300, 'model__min_samples_leaf': 5, 'model__max_depth': None}</t>
         </is>
       </c>
     </row>
@@ -712,7 +712,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>RandomForest</t>
+          <t>XGBoost</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -721,50 +721,50 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.6461</v>
+        <v>0.5217000000000001</v>
       </c>
       <c r="E5" t="n">
-        <v>0.6056</v>
+        <v>0.7534999999999999</v>
       </c>
       <c r="F5" t="n">
-        <v>0.6487000000000001</v>
+        <v>0.5068</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0999</v>
+        <v>0.0895</v>
       </c>
       <c r="H5" t="n">
-        <v>0.9623</v>
+        <v>0.9696</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1715</v>
+        <v>0.1601</v>
       </c>
       <c r="J5" t="n">
-        <v>0.6607</v>
+        <v>0.6577</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1206</v>
+        <v>0.1174</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0634</v>
+        <v>0.2048</v>
       </c>
       <c r="M5" t="n">
-        <v>0.155</v>
+        <v>0.4757</v>
       </c>
       <c r="N5" t="n">
-        <v>86</v>
+        <v>107</v>
       </c>
       <c r="O5" t="n">
-        <v>775</v>
+        <v>1088</v>
       </c>
       <c r="P5" t="n">
-        <v>1431</v>
+        <v>1118</v>
       </c>
       <c r="Q5" t="n">
-        <v>56</v>
+        <v>35</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>{'model__n_estimators': 300, 'model__min_samples_leaf': 5, 'model__max_depth': None}</t>
+          <t>{'model__subsample': 1.0, 'model__n_estimators': 200, 'model__max_depth': 3, 'model__learning_rate': 0.005, 'model__colsample_bytree': 0.8}</t>
         </is>
       </c>
     </row>
@@ -774,59 +774,59 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>XGBoost</t>
+          <t>RandomForest</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>No synthetic resampling</t>
+          <t>SMOTE</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.4987</v>
+        <v>0.5928</v>
       </c>
       <c r="E6" t="n">
-        <v>0.7746</v>
+        <v>0.6549</v>
       </c>
       <c r="F6" t="n">
-        <v>0.481</v>
+        <v>0.5888</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0876</v>
+        <v>0.093</v>
       </c>
       <c r="H6" t="n">
-        <v>0.9707</v>
+        <v>0.9636</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1575</v>
+        <v>0.1629</v>
       </c>
       <c r="J6" t="n">
-        <v>0.654</v>
+        <v>0.6515</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1181</v>
+        <v>0.1167</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2049</v>
+        <v>0.06759999999999999</v>
       </c>
       <c r="M6" t="n">
-        <v>0.4646</v>
+        <v>0.1548</v>
       </c>
       <c r="N6" t="n">
-        <v>110</v>
+        <v>93</v>
       </c>
       <c r="O6" t="n">
-        <v>1145</v>
+        <v>907</v>
       </c>
       <c r="P6" t="n">
-        <v>1061</v>
+        <v>1299</v>
       </c>
       <c r="Q6" t="n">
-        <v>32</v>
+        <v>49</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>{'model__subsample': 1.0, 'model__n_estimators': 200, 'model__max_depth': 3, 'model__learning_rate': 0.005, 'model__colsample_bytree': 0.8}</t>
+          <t>{'model__n_estimators': 300, 'model__min_samples_leaf': 5, 'model__max_depth': None}</t>
         </is>
       </c>
     </row>
